--- a/product_upload/packages/49/file.xlsx
+++ b/product_upload/packages/49/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -836,6 +841,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>ARTELAC COMPLETE SDU EYE DROP</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-EAAB82F54C2D</t>
         </is>
       </c>
@@ -859,7 +869,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1018,6 +1028,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>Rozlytrek</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-A510B1772275</t>
         </is>
       </c>
@@ -1041,7 +1056,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1204,6 +1219,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>Rozlytrek</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-D7EFFDB61A87</t>
         </is>
       </c>
@@ -1227,7 +1247,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1390,6 +1410,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>Lojuxta</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-62C35A13F5BA</t>
         </is>
       </c>
@@ -1413,7 +1438,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1580,6 +1605,11 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>Lojuxta</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-6362B752CF5F</t>
         </is>
       </c>
@@ -1603,7 +1633,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1770,6 +1800,11 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>Lojuxta</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-8FFB1787C9F2</t>
         </is>
       </c>
@@ -1793,7 +1828,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1956,6 +1991,11 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>Kepavie</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-DB96A4EF0BBB</t>
         </is>
       </c>
@@ -1979,7 +2019,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2134,6 +2174,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>Artelac Ectoin SDU</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-CC317981CDB0</t>
         </is>
       </c>
@@ -2157,7 +2202,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2322,6 +2367,11 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>Zorta</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-C57E08BF20F9</t>
         </is>
       </c>
@@ -2345,7 +2395,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2508,6 +2558,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>Dicynone</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-22377E26C90B</t>
         </is>
       </c>
@@ -2531,7 +2586,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2702,6 +2757,11 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>Crinone</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-B2E90FD7FD9F</t>
         </is>
       </c>
@@ -2725,7 +2785,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2886,6 +2946,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>Starkoprex</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-F3459036761B</t>
         </is>
       </c>
@@ -2909,7 +2974,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3076,6 +3141,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>Dusta plus</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-A144A3199B81</t>
         </is>
       </c>
@@ -3099,7 +3169,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3254,6 +3324,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>Clavodar ES Suspension</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-D3D4035443BC</t>
         </is>
       </c>
@@ -3277,7 +3352,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3448,6 +3523,11 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>Fedlora</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-0165A0279C28</t>
         </is>
       </c>
@@ -3471,7 +3551,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3638,6 +3718,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t xml:space="preserve">MONTEK 4 mg </t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-1488350A5F6B</t>
         </is>
       </c>
@@ -3661,7 +3746,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3832,6 +3917,11 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
+          <t xml:space="preserve">MONTEK 5 mg </t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-312175A8C7B2</t>
         </is>
       </c>
@@ -3855,7 +3945,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4018,6 +4108,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t xml:space="preserve">MONTEK 10 mg </t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-E6C57686A65A</t>
         </is>
       </c>
@@ -4041,7 +4136,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4214,6 +4309,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>Axepta</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-4B96D9058C99</t>
         </is>
       </c>
@@ -4237,7 +4337,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4408,6 +4508,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>LOTEMAX 0.5% GEL</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-38DF33FDB782</t>
         </is>
       </c>
@@ -4431,7 +4536,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4600,6 +4705,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>Axepta</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-DFC9F46AC747</t>
         </is>
       </c>
@@ -4623,7 +4733,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4796,6 +4906,11 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>Axepta</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-8ECF619FB654</t>
         </is>
       </c>
@@ -4819,7 +4934,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4988,6 +5103,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>Axepta</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-827150FC9B4D</t>
         </is>
       </c>
@@ -5011,7 +5131,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5184,6 +5304,11 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>Axepta</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-9B597FE2523A</t>
         </is>
       </c>
@@ -5207,7 +5332,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5374,6 +5499,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>Gizlan HCT</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-31F884EB964B</t>
         </is>
       </c>
@@ -5397,7 +5527,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5568,6 +5698,11 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>Gizlan HCT</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-ECCA25B2D4CB</t>
         </is>
       </c>
@@ -5591,7 +5726,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5754,6 +5889,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>Amstar</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-36438619E95A</t>
         </is>
       </c>
@@ -5777,7 +5917,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5944,6 +6084,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>Amstar</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-99BF0B4797B5</t>
         </is>
       </c>
@@ -5967,7 +6112,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6142,6 +6287,11 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>Enstilar</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-B5442B904606</t>
         </is>
       </c>
@@ -6165,7 +6315,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6340,6 +6490,11 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>JEXT</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-190381BEAD20</t>
         </is>
       </c>
@@ -6363,7 +6518,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6538,6 +6693,11 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>JEXT</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-3C9F2716F3D7</t>
         </is>
       </c>
@@ -6561,7 +6721,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6740,6 +6900,11 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>VelExel</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-D235EE629DE9</t>
         </is>
       </c>
@@ -6763,7 +6928,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6938,6 +7103,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>VelExel</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-FD75ADC93347</t>
         </is>
       </c>
@@ -6961,7 +7131,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7128,6 +7298,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>NEUCYTE</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-7EF3E56D9918</t>
         </is>
       </c>
@@ -7151,7 +7326,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7322,6 +7497,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>ENDOSA 2000IU PRE-FILLED SYRINGE</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-B6490BFD1425</t>
         </is>
       </c>
@@ -7345,7 +7525,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7516,6 +7696,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>ENDOSA 4000IU PRE-FILLED SYRINGE</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-370377AE4FF5</t>
         </is>
       </c>
@@ -7539,7 +7724,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7714,6 +7899,11 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>ENDOSA 6000IU PRE-FILLED SYRINGE</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-EF30C2A68E54</t>
         </is>
       </c>
@@ -7737,7 +7927,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7908,6 +8098,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>ENDOSA 8000IU PRE-FILLED SYRINGE</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-B9F8A2890CF6</t>
         </is>
       </c>
@@ -7931,7 +8126,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8094,6 +8289,11 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>Penetro</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-A2BC0379B00F</t>
         </is>
       </c>
@@ -8117,7 +8317,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8280,6 +8480,11 @@
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>HADLIMA 40MG/0.8ML INJECTION IN PFP</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-BA26F19BEBC0</t>
         </is>
       </c>
@@ -8303,7 +8508,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8466,6 +8671,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t xml:space="preserve">HADLIMA 40MG/0.8ML INJECTION IN PRE-FILLED SYRING	</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-7B268FFE8981</t>
         </is>
       </c>
@@ -8489,7 +8699,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8646,6 +8856,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>TYKODAS</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-DA5A6418492B</t>
         </is>
       </c>
@@ -8669,7 +8884,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8840,6 +9055,11 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>Avotrene Emulgel</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-CD5836E113FA</t>
         </is>
       </c>
@@ -8863,7 +9083,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -9026,6 +9246,11 @@
       </c>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>Lepica</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-8A07C166E67B</t>
         </is>
       </c>
@@ -9049,7 +9274,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9212,6 +9437,11 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>Lepica</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-8E004BB7A083</t>
         </is>
       </c>
@@ -9235,7 +9465,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9402,6 +9632,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>ENTYVIO</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-B2AC9B47ED8F</t>
         </is>
       </c>
@@ -9425,7 +9660,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9596,6 +9831,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>ENTYVIO</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-6DCDDC5549D2</t>
         </is>
       </c>
@@ -9619,7 +9859,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9782,6 +10022,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>Zavoxa</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-E4583BBF2EF0</t>
         </is>
       </c>
@@ -9805,7 +10050,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9968,6 +10213,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>LYUMJEV Kwikpen</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-59033B63E935</t>
         </is>
       </c>
@@ -9991,7 +10241,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10158,6 +10408,11 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>LYUMJEV Junior Kwikpen</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-D54AF193ECC1</t>
         </is>
       </c>
@@ -10181,7 +10436,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10344,6 +10599,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>LYUMJEV</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-0B0D89A039B7</t>
         </is>
       </c>
@@ -10367,7 +10627,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10534,6 +10794,11 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>Lyumjev KwikPen</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-7F30C43ACEF8</t>
         </is>
       </c>
@@ -10557,7 +10822,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10722,6 +10987,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>ATIQUIX</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-15D6402AA790</t>
         </is>
       </c>
@@ -10745,7 +11015,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10914,6 +11184,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>ATIQUIX</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-699BEB8D16A0</t>
         </is>
       </c>
@@ -10937,7 +11212,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11104,6 +11379,11 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>Amaglime-Met</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-328053A90DA5</t>
         </is>
       </c>
@@ -11127,7 +11407,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11294,6 +11574,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>Trepadio</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-23D436DE1BEF</t>
         </is>
       </c>
@@ -11317,7 +11602,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11488,6 +11773,11 @@
       </c>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>Trepadio</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-DF0F968ECC06</t>
         </is>
       </c>
@@ -11511,7 +11801,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11674,6 +11964,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>Trepadio</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-0CA5B9E4E213</t>
         </is>
       </c>
@@ -11697,7 +11992,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11860,6 +12155,11 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>Kerendia</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-9EB996AAEF7B</t>
         </is>
       </c>
@@ -11883,7 +12183,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12046,6 +12346,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>Enerzair Breezhaler</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-32BA93D687D0</t>
         </is>
       </c>
@@ -12069,7 +12374,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12228,6 +12533,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>Sulmetic</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-6A6112144B65</t>
         </is>
       </c>
@@ -12251,7 +12561,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12414,6 +12724,11 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>Sulmetic</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-143D8A503BE0</t>
         </is>
       </c>
@@ -12437,7 +12752,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12602,6 +12917,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>Pulmirema 0.25 mg</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-BAB3920DA2CC</t>
         </is>
       </c>
@@ -12625,7 +12945,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12786,6 +13106,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>Pulmirema 0.5 mg</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-1A3356320E3E</t>
         </is>
       </c>
@@ -12809,7 +13134,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12982,6 +13307,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>Pulmirema 1 mg</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-27E119C1EB31</t>
         </is>
       </c>
@@ -13005,7 +13335,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13162,6 +13492,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>Sermitor</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-C8621ABFF232</t>
         </is>
       </c>
@@ -13185,7 +13520,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13344,6 +13679,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>VITAROS 3MG/GM CREAM</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-8906F02225B5</t>
         </is>
       </c>
@@ -13367,7 +13707,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13538,6 +13878,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>VASCEPA 1GM CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-67F5FD004C90</t>
         </is>
       </c>
@@ -13561,7 +13906,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13720,6 +14065,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>Dorius</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-7725E40397FF</t>
         </is>
       </c>
@@ -13743,7 +14093,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13914,6 +14264,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>RYALTRIS</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-F4212146EFBC</t>
         </is>
       </c>
@@ -13937,7 +14292,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14102,6 +14457,11 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>Platica</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-BBEFC99CD0EF</t>
         </is>
       </c>
@@ -14125,7 +14485,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14292,6 +14652,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>Nicorette</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-AD687EA01113</t>
         </is>
       </c>
@@ -14315,7 +14680,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14486,6 +14851,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>Nicorette</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-B62ABFA6C836</t>
         </is>
       </c>
@@ -14509,7 +14879,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14680,6 +15050,11 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>Nicorette</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-EA645E14C0BC</t>
         </is>
       </c>
@@ -14703,7 +15078,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14870,6 +15245,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>Trepadio</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-C0102D563077</t>
         </is>
       </c>
@@ -14893,7 +15273,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15060,6 +15440,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>Trepadio</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-5EE06FBAEE5A</t>
         </is>
       </c>
@@ -15083,7 +15468,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15260,6 +15645,11 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>Helt</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-E1951F637F12</t>
         </is>
       </c>
@@ -15283,7 +15673,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15450,6 +15840,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t xml:space="preserve">VITRAM Oral Solution </t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-869505AA56BB</t>
         </is>
       </c>
@@ -15473,7 +15868,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15644,6 +16039,11 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>CANDAN</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-5DE878CB8884</t>
         </is>
       </c>
@@ -15667,7 +16067,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15836,6 +16236,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>Vaprena</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-39439688F20F</t>
         </is>
       </c>
@@ -15859,7 +16264,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -16032,6 +16437,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>Vaprena</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-36F2268DF119</t>
         </is>
       </c>
@@ -16055,7 +16465,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16214,6 +16624,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>Lodiab XR</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-46D99334A1B0</t>
         </is>
       </c>
@@ -16237,7 +16652,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16400,6 +16815,11 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>Lodiab XR</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-7DA65411204B</t>
         </is>
       </c>
@@ -16423,7 +16843,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16590,6 +17010,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>Lodiab XR</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-7AF51CA7C7A5</t>
         </is>
       </c>
@@ -16613,7 +17038,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16776,6 +17201,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>Lodiab XR</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-B659BC352BCC</t>
         </is>
       </c>
@@ -16799,7 +17229,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16958,6 +17388,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>Lodiab XR</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-3D5C72F8AFFA</t>
         </is>
       </c>
@@ -16981,7 +17416,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17140,6 +17575,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>Lodiab XR</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-1199EF705C16</t>
         </is>
       </c>
@@ -17163,7 +17603,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17334,6 +17774,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>Baclon</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-7CDA00ECA0B9</t>
         </is>
       </c>
@@ -17357,7 +17802,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17528,6 +17973,11 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>Baclon</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-6B3509B87601</t>
         </is>
       </c>
@@ -17551,7 +18001,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17722,6 +18172,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>Sogroya 10 mg / 1.5 ml</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-A12A0832B418</t>
         </is>
       </c>
@@ -17745,7 +18200,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17916,6 +18371,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>GLYXAMBI</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-E2903E8F69D2</t>
         </is>
       </c>
@@ -17939,7 +18399,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18118,6 +18578,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>GLYXAMBI</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-355AEC3AA8F9</t>
         </is>
       </c>
@@ -18141,7 +18606,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18308,6 +18773,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>FEMIC</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-D8C001F18391</t>
         </is>
       </c>
@@ -18331,7 +18801,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18490,6 +18960,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>Serova</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-673CD3B0FA18</t>
         </is>
       </c>
@@ -18513,7 +18988,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18672,6 +19147,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>Serova</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-F1E32E0B429B</t>
         </is>
       </c>
@@ -18695,7 +19175,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18858,6 +19338,11 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>Serova</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-2FD6735DEF17</t>
         </is>
       </c>
@@ -18881,7 +19366,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -19044,6 +19529,11 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>Verquvo</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-1482B596688A</t>
         </is>
       </c>
@@ -19067,7 +19557,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19226,6 +19716,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>Verquvo</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-DDCF9EBA6595</t>
         </is>
       </c>
@@ -19249,7 +19744,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19408,6 +19903,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>Verquvo</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-E7A23F5E616E</t>
         </is>
       </c>
@@ -19431,7 +19931,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19597,6 +20097,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>Formit XR</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-14B71228F39F</t>
         </is>
@@ -19613,7 +20118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19659,100 +20164,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19784,7 +20294,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19799,92 +20309,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-71645</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>209.56</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>463</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19916,7 +20431,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19931,92 +20446,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-43853</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>380.35</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>464</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20048,7 +20568,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20063,92 +20583,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-69926</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>455.39</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>465</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20180,7 +20705,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20195,92 +20720,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-78012</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>402.79</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>466</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20312,7 +20842,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20327,92 +20857,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-11576</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>479.22</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>467</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20444,7 +20979,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20459,92 +20994,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-29100</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>298.86</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>468</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20576,7 +21116,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20591,92 +21131,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-62229</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>451.82</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>469</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20708,7 +21253,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20723,92 +21268,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-63745</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>159.67</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>470</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20840,7 +21390,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20855,92 +21405,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-85448</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>343.39</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>471</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20972,7 +21527,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20987,92 +21542,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-24353</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>20.78</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>472</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21104,7 +21664,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21119,92 +21679,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-41537</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>32.68</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>473</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21221,7 +21786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21327,6 +21892,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21362,7 +21937,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21427,6 +22002,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-6B0403A942D7</t>
         </is>
@@ -21463,7 +22048,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21528,6 +22113,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-4AB669718E15</t>
         </is>
@@ -21564,7 +22159,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21629,6 +22224,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-C6076F803E0B</t>
         </is>
@@ -21665,7 +22270,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21730,6 +22335,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-6E5C8B15FF44</t>
         </is>
@@ -21766,7 +22381,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21831,6 +22446,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-514928FDF435</t>
         </is>
@@ -21867,7 +22492,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21932,6 +22557,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-54F4434A0F01</t>
         </is>
@@ -21968,7 +22603,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22033,6 +22668,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-891C1C773394</t>
         </is>
@@ -22069,7 +22714,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22134,6 +22779,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-F2154405E7BB</t>
         </is>
@@ -22170,7 +22825,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22235,6 +22890,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-CA847FA0AB33</t>
         </is>
@@ -22271,7 +22936,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22336,6 +23001,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-56A7ECBE9EA1</t>
         </is>
@@ -22372,7 +23047,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22437,6 +23112,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-8E8A0DD41B5C</t>
         </is>
@@ -22473,7 +23158,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22538,6 +23223,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-0C63885C9B1C</t>
         </is>
@@ -22574,7 +23269,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22639,6 +23334,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-9AE93770159A</t>
         </is>
@@ -22675,7 +23380,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22740,6 +23445,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-3BDDBC321833</t>
         </is>
@@ -22776,7 +23491,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22841,6 +23556,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-38BC4869B868</t>
         </is>
@@ -22877,7 +23602,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22942,6 +23667,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-A440BCE56971</t>
         </is>
@@ -22978,7 +23713,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23043,6 +23778,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-40E8874A2124</t>
         </is>
@@ -23079,7 +23824,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23144,6 +23889,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-017453F11506</t>
         </is>
@@ -23180,7 +23935,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23245,6 +24000,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-D3A3D4BA3CBE</t>
         </is>
@@ -23281,7 +24046,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23346,6 +24111,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-FFEA3263FC29</t>
         </is>

--- a/product_upload/packages/49/file.xlsx
+++ b/product_upload/packages/49/file.xlsx
@@ -877,8 +877,16 @@
           <t>2903946362-491-808905384442</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rozlytrek</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Rozlytrek detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1064,8 +1072,16 @@
           <t>2544252967-213-106884721815</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rozlytrek</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Rozlytrek detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1255,8 +1271,16 @@
           <t>2669031354-258-982258256469</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lojuxta</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Lojuxta detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1446,8 +1470,16 @@
           <t>3158308045-409-353031006807</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lojuxta</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Lojuxta detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1641,8 +1673,16 @@
           <t>2270842094-548-901215748176</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lojuxta</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Lojuxta detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1836,8 +1876,16 @@
           <t>2136862466-104-727441876099</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Kepavie</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kepavie detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -2027,8 +2075,16 @@
           <t>6462669688-564-654701373482</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Artelac Ectoin SDU</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Artelac Ectoin SDU detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2210,8 +2266,16 @@
           <t>7014330490-105-527033663247</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zorta</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Zorta detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -2403,8 +2467,16 @@
           <t>1206209523-262-173134975176</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dicynone</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Dicynone detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2594,8 +2666,16 @@
           <t>5094574806-010-599149201195</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Crinone</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Crinone detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2793,8 +2873,16 @@
           <t>1061630347-529-400938999948</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Starkoprex</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Starkoprex detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -3177,8 +3265,16 @@
           <t>5023560783-008-869322843078</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Clavodar ES Suspension</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Clavodar ES Suspension detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -5734,8 +5830,16 @@
           <t>9454074185-635-725443746334</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Amstar</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Amstar detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -5925,8 +6029,16 @@
           <t>1003492249-094-329518331521</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Amstar</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Amstar detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -7139,8 +7251,16 @@
           <t>8319906606-668-941142128100</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NEUCYTE</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>NEUCYTE detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -8134,8 +8254,16 @@
           <t>0400025182-315-712084305450</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Penetro</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Penetro detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -8325,8 +8453,16 @@
           <t>6853622622-869-739686617304</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HADLIMA 40MG/0.8ML INJECTION IN PFP</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>HADLIMA 40MG/0.8ML INJECTION IN PFP detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8516,8 +8652,16 @@
           <t>2026079436-659-079869310961</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HADLIMA 40MG/0.8ML INJECTION IN PRE-FILLED SYRING</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>HADLIMA 40MG/0.8ML INJECTION IN PRE-FILLED SYRING detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8707,8 +8851,16 @@
           <t>1249964302-850-017871529553</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TYKODAS</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>TYKODAS detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -9091,8 +9243,16 @@
           <t>9217432544-783-611326001817</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lepica</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Lepica detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -9282,8 +9442,16 @@
           <t>0684047752-213-990661879211</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lepica</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Lepica detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9867,8 +10035,16 @@
           <t>5124926630-516-516220937564</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zavoxa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Zavoxa detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -10058,8 +10234,16 @@
           <t>8432402109-996-579257690453</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LYUMJEV Kwikpen</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>LYUMJEV Kwikpen detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -10249,8 +10433,16 @@
           <t>5033855436-508-665386441458</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LYUMJEV Junior Kwikpen</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>LYUMJEV Junior Kwikpen detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10444,8 +10636,16 @@
           <t>2400253356-567-629017473765</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LYUMJEV</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>LYUMJEV detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10635,8 +10835,16 @@
           <t>0474125558-979-919816825422</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lyumjev KwikPen</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Lyumjev KwikPen detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -11220,8 +11428,16 @@
           <t>8321598819-264-473104135007</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Amaglime-Met</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Amaglime-Met detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -12191,8 +12407,16 @@
           <t>9206529474-871-628085559039</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Enerzair Breezhaler</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Enerzair Breezhaler detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12382,8 +12606,16 @@
           <t>5732532836-884-573684894799</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sulmetic</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sulmetic detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12569,8 +12801,16 @@
           <t>7633718150-066-849926240301</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sulmetic</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sulmetic detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12760,8 +13000,16 @@
           <t>5446852920-162-978051793478</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pulmirema 0.25 mg</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Pulmirema 0.25 mg detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
           <t>Sudair Pharma Company</t>
@@ -12953,8 +13201,16 @@
           <t>9670061238-881-178240657893</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pulmirema 0.5 mg</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Pulmirema 0.5 mg detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
           <t>Sudair Pharma Company</t>
@@ -13343,8 +13599,16 @@
           <t>4380543630-065-332219461514</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sermitor</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sermitor detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -13528,8 +13792,16 @@
           <t>9320054951-043-098989792172</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VITAROS 3MG/GM CREAM</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>VITAROS 3MG/GM CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13914,8 +14186,16 @@
           <t>1513850006-474-591889814347</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dorius</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Dorius detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -14300,8 +14580,16 @@
           <t>5059097412-332-451452233146</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Platica</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Platica detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
           <t>SAJA-SAUDI ARABIAN JAPANESE PHARMACEUTICAL CO</t>
@@ -16473,8 +16761,16 @@
           <t>9024330981-619-084941943803</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lodiab XR</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Lodiab XR detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -16660,8 +16956,16 @@
           <t>8367996400-769-173820731665</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lodiab XR</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Lodiab XR detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -17046,8 +17350,16 @@
           <t>9199818188-122-845888064994</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lodiab XR</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Lodiab XR detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -17237,8 +17549,16 @@
           <t>5094564862-947-646055758333</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lodiab XR</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Lodiab XR detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17424,8 +17744,16 @@
           <t>2875132042-886-363200059260</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lodiab XR</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Lodiab XR detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -18809,8 +19137,16 @@
           <t>8024031369-828-146738769806</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Serova</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Serova detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -18996,8 +19332,16 @@
           <t>0741939468-485-425445447529</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Serova</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Serova detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -19183,8 +19527,16 @@
           <t>3502806755-543-299035376222</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Serova</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Serova detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -19374,8 +19726,16 @@
           <t>4993623487-191-440150280625</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Verquvo</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Verquvo detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -19565,8 +19925,16 @@
           <t>4654979665-974-476835186145</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Verquvo</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Verquvo detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -19752,8 +20120,16 @@
           <t>2638617147-069-925636454627</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Verquvo</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Verquvo detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/49/file.xlsx
+++ b/product_upload/packages/49/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20540,7 +20540,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22162,7 +22162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22243,40 +22243,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22356,38 +22361,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>177.57</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-6B0403A942D7</t>
         </is>
@@ -22467,38 +22477,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>188.02</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-4AB669718E15</t>
         </is>
@@ -22578,38 +22593,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>23.67</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-C6076F803E0B</t>
         </is>
@@ -22689,38 +22709,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>155.29</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-6E5C8B15FF44</t>
         </is>
@@ -22800,38 +22825,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>144.93</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-514928FDF435</t>
         </is>
@@ -22911,38 +22941,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>289.86</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-54F4434A0F01</t>
         </is>
@@ -23022,38 +23057,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>311.55</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-891C1C773394</t>
         </is>
@@ -23133,38 +23173,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>60.82</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-F2154405E7BB</t>
         </is>
@@ -23244,38 +23289,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>12.26</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-CA847FA0AB33</t>
         </is>
@@ -23355,38 +23405,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>272.99</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-56A7ECBE9EA1</t>
         </is>
@@ -23466,38 +23521,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>479.79</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-8E8A0DD41B5C</t>
         </is>
@@ -23577,38 +23637,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>452.63</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-0C63885C9B1C</t>
         </is>
@@ -23688,38 +23753,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>416.63</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-9AE93770159A</t>
         </is>
@@ -23799,38 +23869,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>96.48</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-3BDDBC321833</t>
         </is>
@@ -23910,38 +23985,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>54.54</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-38BC4869B868</t>
         </is>
@@ -24021,38 +24101,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>440.67</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-A440BCE56971</t>
         </is>
@@ -24132,38 +24217,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>202.04</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-40E8874A2124</t>
         </is>
@@ -24243,38 +24333,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>324.19</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-017453F11506</t>
         </is>
@@ -24354,38 +24449,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>474.58</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-D3A3D4BA3CBE</t>
         </is>
@@ -24465,38 +24565,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>128.56</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-FFEA3263FC29</t>
         </is>
